--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25160" windowHeight="13660"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -62,12 +62,6 @@
   </si>
   <si>
     <t>对应文件名称</t>
-  </si>
-  <si>
-    <t>默认的bgm</t>
-  </si>
-  <si>
-    <t>bgm晒着太阳的懒猫</t>
   </si>
   <si>
     <t>主题bgm</t>
@@ -1204,10 +1198,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="14.5480769230769" customWidth="1"/>
+    <col min="2" max="2" width="14.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1280,7 +1274,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1"/>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
@@ -1289,7 +1283,7 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
+      <c r="A8" s="2"/>
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
@@ -1300,7 +1294,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2"/>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
@@ -1328,17 +1322,15 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:3">
+      <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
+    </row>
+    <row r="13" spans="2:3">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1346,7 +1338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="2:3">
       <c r="B14" t="s">
         <v>29</v>
       </c>
@@ -1354,7 +1346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="2:3">
       <c r="B15" t="s">
         <v>31</v>
       </c>
@@ -1362,7 +1354,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="2:3">
       <c r="B16" t="s">
         <v>33</v>
       </c>
@@ -1523,19 +1515,11 @@
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" t="s">
+      <c r="B36" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C36" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3">
-      <c r="B37" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1549,7 +1533,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1561,7 +1545,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25160" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -70,16 +70,178 @@
     <t>bgm晒着太阳的懒猫</t>
   </si>
   <si>
-    <t>玩家受击</t>
-  </si>
-  <si>
-    <t>s_10</t>
-  </si>
-  <si>
-    <t>玩家死亡</t>
-  </si>
-  <si>
-    <t>s_11</t>
+    <t>UI通用按钮点击</t>
+  </si>
+  <si>
+    <t>s_01</t>
+  </si>
+  <si>
+    <t>UI音量音效条滑动</t>
+  </si>
+  <si>
+    <t>s_03</t>
+  </si>
+  <si>
+    <t>波次三秒倒计时</t>
+  </si>
+  <si>
+    <t>s_04</t>
+  </si>
+  <si>
+    <t>剧情CG弹出</t>
+  </si>
+  <si>
+    <t>s_05</t>
+  </si>
+  <si>
+    <t>玩家投掷开始</t>
+  </si>
+  <si>
+    <t>s_06</t>
+  </si>
+  <si>
+    <t>玩家投掷落地</t>
+  </si>
+  <si>
+    <t>s_07</t>
+  </si>
+  <si>
+    <t>玩家拾取</t>
+  </si>
+  <si>
+    <t>s_08</t>
+  </si>
+  <si>
+    <t>玩家移动</t>
+  </si>
+  <si>
+    <t>s_12</t>
+  </si>
+  <si>
+    <t>玩家丢弃资源</t>
+  </si>
+  <si>
+    <t>s_13</t>
+  </si>
+  <si>
+    <t>地块水蒸气</t>
+  </si>
+  <si>
+    <t>s_14</t>
+  </si>
+  <si>
+    <t>地块结冰</t>
+  </si>
+  <si>
+    <t>s_15</t>
+  </si>
+  <si>
+    <t>地块冰沙</t>
+  </si>
+  <si>
+    <t>s_16</t>
+  </si>
+  <si>
+    <t>地块燃烧</t>
+  </si>
+  <si>
+    <t>s_17</t>
+  </si>
+  <si>
+    <t>地块化为灰烬</t>
+  </si>
+  <si>
+    <t>s_18</t>
+  </si>
+  <si>
+    <t>地块泥浆</t>
+  </si>
+  <si>
+    <t>s_19</t>
+  </si>
+  <si>
+    <t>地块玻璃碎裂</t>
+  </si>
+  <si>
+    <t>s_20</t>
+  </si>
+  <si>
+    <t>地块陶砖</t>
+  </si>
+  <si>
+    <t>s_21</t>
+  </si>
+  <si>
+    <t>地块冻土</t>
+  </si>
+  <si>
+    <t>s_37</t>
+  </si>
+  <si>
+    <t>地块土墙</t>
+  </si>
+  <si>
+    <t>s_38</t>
+  </si>
+  <si>
+    <t>地块荆棘</t>
+  </si>
+  <si>
+    <t>s_22</t>
+  </si>
+  <si>
+    <t>地块导电</t>
+  </si>
+  <si>
+    <t>s_23</t>
+  </si>
+  <si>
+    <t>敌人出生</t>
+  </si>
+  <si>
+    <t>S_024</t>
+  </si>
+  <si>
+    <t>击退敌人</t>
+  </si>
+  <si>
+    <t>s_25</t>
+  </si>
+  <si>
+    <t>敌人受击</t>
+  </si>
+  <si>
+    <t>s_26</t>
+  </si>
+  <si>
+    <t>敌人死亡</t>
+  </si>
+  <si>
+    <t>s_27</t>
+  </si>
+  <si>
+    <t>玩家种植种子</t>
+  </si>
+  <si>
+    <t>s_29</t>
+  </si>
+  <si>
+    <t>玩家回血</t>
+  </si>
+  <si>
+    <t>s_30</t>
+  </si>
+  <si>
+    <t>CG演出车行驶</t>
+  </si>
+  <si>
+    <t>s_28</t>
+  </si>
+  <si>
+    <t>CG演出开车门</t>
+  </si>
+  <si>
+    <t>s_33</t>
   </si>
 </sst>
 </file>
@@ -1024,10 +1186,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="14.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="14.5480769230769" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1110,18 +1272,225 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
       <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1134,7 +1503,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1146,7 +1515,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -68,6 +68,18 @@
   </si>
   <si>
     <t>bgm晒着太阳的懒猫</t>
+  </si>
+  <si>
+    <t>主题bgm</t>
+  </si>
+  <si>
+    <t>bgm_01_main</t>
+  </si>
+  <si>
+    <t>升华bgm</t>
+  </si>
+  <si>
+    <t>bgm_02</t>
   </si>
   <si>
     <t>UI通用按钮点击</t>
@@ -1186,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="14.5480769230769" customWidth="1"/>
@@ -1252,7 +1264,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
@@ -1261,8 +1273,8 @@
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2"/>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
@@ -1271,8 +1283,8 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
@@ -1282,7 +1294,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
@@ -1301,20 +1313,24 @@
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
       </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" t="s">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" t="s">
@@ -1490,6 +1506,22 @@
       </c>
       <c r="C34" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>s_33</t>
+  </si>
+  <si>
+    <t>UI背包按钮滑动</t>
+  </si>
+  <si>
+    <t>s_02</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="14.5480769230769" customWidth="1"/>
@@ -1522,6 +1528,14 @@
       </c>
       <c r="C36" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25160" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -70,16 +70,196 @@
     <t>bgm晒着太阳的懒猫</t>
   </si>
   <si>
-    <t>玩家受击</t>
-  </si>
-  <si>
-    <t>s_10</t>
-  </si>
-  <si>
-    <t>玩家死亡</t>
-  </si>
-  <si>
-    <t>s_11</t>
+    <t>主题bgm</t>
+  </si>
+  <si>
+    <t>bgm_01_main</t>
+  </si>
+  <si>
+    <t>升华bgm</t>
+  </si>
+  <si>
+    <t>bgm_02</t>
+  </si>
+  <si>
+    <t>UI通用按钮点击</t>
+  </si>
+  <si>
+    <t>s_01</t>
+  </si>
+  <si>
+    <t>UI音量音效条滑动</t>
+  </si>
+  <si>
+    <t>s_03</t>
+  </si>
+  <si>
+    <t>波次三秒倒计时</t>
+  </si>
+  <si>
+    <t>s_04</t>
+  </si>
+  <si>
+    <t>剧情CG弹出</t>
+  </si>
+  <si>
+    <t>s_05</t>
+  </si>
+  <si>
+    <t>玩家投掷开始</t>
+  </si>
+  <si>
+    <t>s_06</t>
+  </si>
+  <si>
+    <t>玩家投掷落地</t>
+  </si>
+  <si>
+    <t>s_07</t>
+  </si>
+  <si>
+    <t>玩家拾取</t>
+  </si>
+  <si>
+    <t>s_08</t>
+  </si>
+  <si>
+    <t>玩家移动</t>
+  </si>
+  <si>
+    <t>s_12</t>
+  </si>
+  <si>
+    <t>玩家丢弃资源</t>
+  </si>
+  <si>
+    <t>s_13</t>
+  </si>
+  <si>
+    <t>地块水蒸气</t>
+  </si>
+  <si>
+    <t>s_14</t>
+  </si>
+  <si>
+    <t>地块结冰</t>
+  </si>
+  <si>
+    <t>s_15</t>
+  </si>
+  <si>
+    <t>地块冰沙</t>
+  </si>
+  <si>
+    <t>s_16</t>
+  </si>
+  <si>
+    <t>地块燃烧</t>
+  </si>
+  <si>
+    <t>s_17</t>
+  </si>
+  <si>
+    <t>地块化为灰烬</t>
+  </si>
+  <si>
+    <t>s_18</t>
+  </si>
+  <si>
+    <t>地块泥浆</t>
+  </si>
+  <si>
+    <t>s_19</t>
+  </si>
+  <si>
+    <t>地块玻璃碎裂</t>
+  </si>
+  <si>
+    <t>s_20</t>
+  </si>
+  <si>
+    <t>地块陶砖</t>
+  </si>
+  <si>
+    <t>s_21</t>
+  </si>
+  <si>
+    <t>地块冻土</t>
+  </si>
+  <si>
+    <t>s_37</t>
+  </si>
+  <si>
+    <t>地块土墙</t>
+  </si>
+  <si>
+    <t>s_38</t>
+  </si>
+  <si>
+    <t>地块荆棘</t>
+  </si>
+  <si>
+    <t>s_22</t>
+  </si>
+  <si>
+    <t>地块导电</t>
+  </si>
+  <si>
+    <t>s_23</t>
+  </si>
+  <si>
+    <t>敌人出生</t>
+  </si>
+  <si>
+    <t>S_024</t>
+  </si>
+  <si>
+    <t>击退敌人</t>
+  </si>
+  <si>
+    <t>s_25</t>
+  </si>
+  <si>
+    <t>敌人受击</t>
+  </si>
+  <si>
+    <t>s_26</t>
+  </si>
+  <si>
+    <t>敌人死亡</t>
+  </si>
+  <si>
+    <t>s_27</t>
+  </si>
+  <si>
+    <t>玩家种植种子</t>
+  </si>
+  <si>
+    <t>s_29</t>
+  </si>
+  <si>
+    <t>玩家回血</t>
+  </si>
+  <si>
+    <t>s_30</t>
+  </si>
+  <si>
+    <t>CG演出车行驶</t>
+  </si>
+  <si>
+    <t>s_28</t>
+  </si>
+  <si>
+    <t>CG演出开车门</t>
+  </si>
+  <si>
+    <t>s_33</t>
+  </si>
+  <si>
+    <t>UI背包按钮滑动</t>
+  </si>
+  <si>
+    <t>s_02</t>
   </si>
 </sst>
 </file>
@@ -1024,10 +1204,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="14.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="14.5480769230769" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1090,7 +1270,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
@@ -1099,8 +1279,8 @@
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="2"/>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
@@ -1109,19 +1289,254 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
       <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1134,7 +1549,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1146,7 +1561,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>s_02</t>
+  </si>
+  <si>
+    <t>玩家受伤</t>
+  </si>
+  <si>
+    <t>扣血</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1204,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="14.5454545454545" customWidth="1"/>
@@ -1520,6 +1526,14 @@
       </c>
       <c r="C36" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>扣血</t>
+  </si>
+  <si>
+    <t>玩家冲刺</t>
+  </si>
+  <si>
+    <t>冲刺</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1210,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="14.5454545454545" customWidth="1"/>
@@ -1534,6 +1540,14 @@
       </c>
       <c r="C37" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/audio_map.xlsx
+++ b/ConfigWorkspace/Data/audio_map.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="23120" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -205,7 +205,7 @@
     <t>敌人出生</t>
   </si>
   <si>
-    <t>S_024</t>
+    <t>s_24</t>
   </si>
   <si>
     <t>击退敌人</t>
@@ -260,6 +260,18 @@
   </si>
   <si>
     <t>扣血</t>
+  </si>
+  <si>
+    <t>玩家冲刺</t>
+  </si>
+  <si>
+    <t>s_36</t>
+  </si>
+  <si>
+    <t>死亡失败结算</t>
+  </si>
+  <si>
+    <t>s_35</t>
   </si>
 </sst>
 </file>
@@ -1204,10 +1216,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="14.5454545454545" customWidth="1"/>
+    <col min="2" max="2" width="14.5480769230769" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1328,7 +1340,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:3">
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>25</v>
       </c>
@@ -1336,7 +1348,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="2:3">
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1344,7 +1356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="2:3">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
         <v>29</v>
       </c>
@@ -1352,7 +1364,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="2:3">
+    <row r="15" spans="1:4">
       <c r="B15" t="s">
         <v>31</v>
       </c>
@@ -1360,7 +1372,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:3">
+    <row r="16" spans="1:4">
       <c r="B16" t="s">
         <v>33</v>
       </c>
@@ -1534,6 +1546,22 @@
       </c>
       <c r="C37" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1547,7 +1575,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1559,7 +1587,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
